--- a/s2-charts-exploration/follow-along.xlsx
+++ b/s2-charts-exploration/follow-along.xlsx
@@ -611,14 +611,14 @@
     <row r="1" ht="28" customHeight="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Session 2: Charts and exploration Excel can't do alone</t>
+          <t>Session 2: Charts and exploration with seaborn</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Get a Python chart out of the cell, then make five more Excel can't.  (45 min, free live session 2 of 4)</t>
+          <t>Your first seaborn chart, then five more, one line of code each.  (45 min, free live session 2 of 4)</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
     <row r="45" ht="22" customHeight="1">
       <c r="B45" s="9" t="inlineStr">
         <is>
-          <t>Part 2: Charts Excel doesn't have  (~13 min)</t>
+          <t>Part 2: Five charts, one line each  (~13 min)</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <row r="63" ht="51" customHeight="1">
       <c r="B63" s="10" t="inlineStr">
         <is>
-          <t>The Excel way: Insert, Statistic Chart, Box and Whisker, which exists but cannot take a category column directly; you reshape the data first. Click K60, Ctrl+Alt+Shift+P, one line. Ctrl+Enter, Ctrl+Alt+Shift+M, Create Reference.</t>
+          <t>The Excel way: Insert, Statistic Chart, Box and Whisker, which exists but wants the data reshaped first, one column per group. Click K60, Ctrl+Alt+Shift+P, one line. Ctrl+Enter, Ctrl+Alt+Shift+M, Create Reference.</t>
         </is>
       </c>
     </row>
